--- a/commodity-risk-dashboard/data/commodities_powerbi.xlsx
+++ b/commodity-risk-dashboard/data/commodities_powerbi.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1510"/>
+  <dimension ref="A1:O1511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39832,7 +39832,7 @@
     </row>
     <row r="755">
       <c r="A755" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
@@ -39848,34 +39848,34 @@
         <v>0</v>
       </c>
       <c r="E755" t="n">
-        <v>78.93000030517578</v>
+        <v>81.06999969482422</v>
       </c>
       <c r="F755" t="n">
-        <v>77.23000335693359</v>
+        <v>80.01000213623047</v>
       </c>
       <c r="G755" t="n">
-        <v>80.12999725341797</v>
+        <v>80.11000061035156</v>
       </c>
       <c r="H755" t="n">
-        <v>11846</v>
+        <v>13608</v>
       </c>
       <c r="I755" t="n">
-        <v>3.420229454916801</v>
+        <v>3.394420675618903</v>
       </c>
       <c r="J755" t="n">
-        <v>0.3312876839875374</v>
+        <v>0.3309418709895202</v>
       </c>
       <c r="K755" t="n">
-        <v>-0.2225672116942696</v>
+        <v>-0.2227612220088676</v>
       </c>
       <c r="L755" t="n">
-        <v>-0.1261723018524703</v>
+        <v>-0.1263903677601245</v>
       </c>
       <c r="M755" t="n">
-        <v>82.28159973144531</v>
+        <v>82.28119979858398</v>
       </c>
       <c r="N755" t="n">
-        <v>73.89394998550415</v>
+        <v>73.89385000228881</v>
       </c>
       <c r="O755" t="inlineStr">
         <is>
@@ -79291,30 +79291,83 @@
         <v>292.0499877929688</v>
       </c>
       <c r="G1510" t="n">
+        <v>292.7000122070312</v>
+      </c>
+      <c r="H1510" t="n">
+        <v>18777</v>
+      </c>
+      <c r="I1510" t="n">
+        <v>-3.859418469002984</v>
+      </c>
+      <c r="J1510" t="n">
+        <v>0.366619132707929</v>
+      </c>
+      <c r="K1510" t="n">
+        <v>-0.3331054539133458</v>
+      </c>
+      <c r="L1510" t="n">
+        <v>-0.3075467145629706</v>
+      </c>
+      <c r="M1510" t="n">
+        <v>320.0939996337891</v>
+      </c>
+      <c r="N1510" t="n">
+        <v>310.3020001983643</v>
+      </c>
+      <c r="O1510" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>KC=F</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>Coffee (Arabica)</t>
+        </is>
+      </c>
+      <c r="D1511" t="n">
         <v>293.8999938964844</v>
       </c>
-      <c r="H1510" t="n">
+      <c r="E1511" t="n">
+        <v>294.8999938964844</v>
+      </c>
+      <c r="F1511" t="n">
+        <v>286</v>
+      </c>
+      <c r="G1511" t="n">
+        <v>287.8500061035156</v>
+      </c>
+      <c r="H1511" t="n">
         <v>0</v>
       </c>
-      <c r="I1510" t="n">
-        <v>-3.465271107748447</v>
-      </c>
-      <c r="J1510" t="n">
-        <v>0.3621258964421938</v>
-      </c>
-      <c r="K1510" t="n">
-        <v>-0.3303713875972361</v>
-      </c>
-      <c r="L1510" t="n">
-        <v>-0.3047078651312242</v>
-      </c>
-      <c r="M1510" t="n">
-        <v>320.1179992675781</v>
-      </c>
-      <c r="N1510" t="n">
-        <v>310.3080001068115</v>
-      </c>
-      <c r="O1510" t="inlineStr">
+      <c r="I1511" t="n">
+        <v>-1.656988691918859</v>
+      </c>
+      <c r="J1511" t="n">
+        <v>0.3685045237625176</v>
+      </c>
+      <c r="K1511" t="n">
+        <v>-0.3441558211290252</v>
+      </c>
+      <c r="L1511" t="n">
+        <v>-0.3190205871994827</v>
+      </c>
+      <c r="M1511" t="n">
+        <v>319.335</v>
+      </c>
+      <c r="N1511" t="n">
+        <v>310.0380002593994</v>
+      </c>
+      <c r="O1511" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
@@ -84958,23 +85011,23 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>293.9</v>
+        <v>287.85</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.47</v>
+        <v>-1.66</v>
       </c>
       <c r="J2" t="n">
-        <v>36.2</v>
+        <v>36.9</v>
       </c>
       <c r="K2" t="n">
-        <v>-33</v>
+        <v>-34.4</v>
       </c>
       <c r="L2" t="n">
-        <v>-30.5</v>
+        <v>-31.9</v>
       </c>
       <c r="M2" t="n">
         <v>422.7</v>
@@ -84988,7 +85041,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>110212</v>
+        <v>107944</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.01</v>
@@ -85025,14 +85078,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>80.13</v>
+        <v>80.11</v>
       </c>
       <c r="I3" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="J3" t="n">
         <v>33.1</v>
@@ -85055,7 +85108,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>40065</v>
+        <v>40055</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.01</v>

--- a/commodity-risk-dashboard/data/commodities_powerbi.xlsx
+++ b/commodity-risk-dashboard/data/commodities_powerbi.xlsx
@@ -39832,7 +39832,7 @@
     </row>
     <row r="755">
       <c r="A755" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
@@ -39854,28 +39854,28 @@
         <v>80.01000213623047</v>
       </c>
       <c r="G755" t="n">
-        <v>80.12000274658203</v>
+        <v>80.19000244140625</v>
       </c>
       <c r="H755" t="n">
-        <v>17419</v>
+        <v>13876</v>
       </c>
       <c r="I755" t="n">
-        <v>-0.6694779209153623</v>
+        <v>-0.5826942714656891</v>
       </c>
       <c r="J755" t="n">
-        <v>0.3488064664651024</v>
+        <v>0.3486119620823286</v>
       </c>
       <c r="K755" t="n">
-        <v>-0.2226641798408256</v>
+        <v>-0.2219850327075039</v>
       </c>
       <c r="L755" t="n">
-        <v>-0.1262812932065439</v>
+        <v>-0.1255179377304938</v>
       </c>
       <c r="M755" t="n">
-        <v>82.28199996948243</v>
+        <v>82.28339996337891</v>
       </c>
       <c r="N755" t="n">
-        <v>74.29090003967285</v>
+        <v>74.29125003814697</v>
       </c>
       <c r="O755" t="inlineStr">
         <is>
@@ -79322,7 +79322,7 @@
     </row>
     <row r="1511">
       <c r="A1511" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
@@ -79335,37 +79335,37 @@
         </is>
       </c>
       <c r="D1511" t="n">
-        <v>296.6499938964844</v>
+        <v>299.25</v>
       </c>
       <c r="E1511" t="n">
-        <v>298.8500061035156</v>
+        <v>311.2999877929688</v>
       </c>
       <c r="F1511" t="n">
-        <v>291.9500122070312</v>
+        <v>298.3500061035156</v>
       </c>
       <c r="G1511" t="n">
-        <v>298.7000122070312</v>
+        <v>305.5499877929688</v>
       </c>
       <c r="H1511" t="n">
-        <v>0</v>
+        <v>25328</v>
       </c>
       <c r="I1511" t="n">
-        <v>0.2180924142543672</v>
+        <v>2.516356419115051</v>
       </c>
       <c r="J1511" t="n">
-        <v>0.360937998651592</v>
+        <v>0.3707680196581545</v>
       </c>
       <c r="K1511" t="n">
-        <v>-0.3194349137369085</v>
+        <v>-0.3038277693277128</v>
       </c>
       <c r="L1511" t="n">
-        <v>-0.2933522508139104</v>
+        <v>-0.2771469624578209</v>
       </c>
       <c r="M1511" t="n">
-        <v>316.1860003662109</v>
+        <v>316.3229998779297</v>
       </c>
       <c r="N1511" t="n">
-        <v>308.669750289917</v>
+        <v>308.7040001678467</v>
       </c>
       <c r="O1511" t="inlineStr">
         <is>
@@ -84971,23 +84971,23 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>298.7</v>
+        <v>305.55</v>
       </c>
       <c r="I2" t="n">
-        <v>0.22</v>
+        <v>2.52</v>
       </c>
       <c r="J2" t="n">
-        <v>36.1</v>
+        <v>37.1</v>
       </c>
       <c r="K2" t="n">
-        <v>-31.9</v>
+        <v>-30.4</v>
       </c>
       <c r="L2" t="n">
-        <v>-29.3</v>
+        <v>-27.7</v>
       </c>
       <c r="M2" t="n">
         <v>422.7</v>
@@ -85001,7 +85001,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>112013</v>
+        <v>114581</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.01</v>
@@ -85038,20 +85038,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>80.12</v>
+        <v>80.19</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.67</v>
+        <v>-0.58</v>
       </c>
       <c r="J3" t="n">
         <v>34.9</v>
       </c>
       <c r="K3" t="n">
-        <v>-22.3</v>
+        <v>-22.2</v>
       </c>
       <c r="L3" t="n">
         <v>-12.6</v>
@@ -85068,7 +85068,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>40060</v>
+        <v>40095</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.01</v>
